--- a/output/yearly_population_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_38_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6881</v>
+        <v>5688</v>
       </c>
       <c r="C2" t="n">
-        <v>4598</v>
+        <v>6347</v>
       </c>
       <c r="D2" t="n">
-        <v>32725</v>
+        <v>36220</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3627</v>
+        <v>3111</v>
       </c>
       <c r="C3" t="n">
-        <v>5131</v>
+        <v>4880</v>
       </c>
       <c r="D3" t="n">
-        <v>16042</v>
+        <v>19582</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2775</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>4739</v>
+        <v>6198</v>
       </c>
       <c r="D4" t="n">
-        <v>6913</v>
+        <v>9526</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1767</v>
+        <v>1517</v>
       </c>
       <c r="C5" t="n">
-        <v>4241</v>
+        <v>5765</v>
       </c>
       <c r="D5" t="n">
-        <v>2461</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1028</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>2620</v>
+        <v>3833</v>
       </c>
       <c r="D6" t="n">
-        <v>1108</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491</v>
+        <v>374</v>
       </c>
       <c r="C7" t="n">
-        <v>1263</v>
+        <v>2345</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>520</v>
+        <v>1144</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7170</v>
+        <v>5579</v>
       </c>
       <c r="C2" t="n">
-        <v>9608</v>
+        <v>7297</v>
       </c>
       <c r="D2" t="n">
-        <v>32191</v>
+        <v>35739</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4128</v>
+        <v>3391</v>
       </c>
       <c r="C3" t="n">
-        <v>4277</v>
+        <v>4869</v>
       </c>
       <c r="D3" t="n">
-        <v>17340</v>
+        <v>20427</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2700</v>
+        <v>2287</v>
       </c>
       <c r="C4" t="n">
-        <v>4836</v>
+        <v>5474</v>
       </c>
       <c r="D4" t="n">
-        <v>8280</v>
+        <v>10781</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1972</v>
+        <v>1665</v>
       </c>
       <c r="C5" t="n">
-        <v>4351</v>
+        <v>5776</v>
       </c>
       <c r="D5" t="n">
-        <v>3112</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1232</v>
+        <v>996</v>
       </c>
       <c r="C6" t="n">
-        <v>3355</v>
+        <v>4613</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>651</v>
+        <v>492</v>
       </c>
       <c r="C7" t="n">
-        <v>1875</v>
+        <v>2933</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="C8" t="n">
-        <v>854</v>
+        <v>1614</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>727</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10205</v>
+        <v>6502</v>
       </c>
       <c r="C2" t="n">
-        <v>6293</v>
+        <v>8433</v>
       </c>
       <c r="D2" t="n">
-        <v>34586</v>
+        <v>41483</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4439</v>
+        <v>3440</v>
       </c>
       <c r="C3" t="n">
-        <v>5788</v>
+        <v>5162</v>
       </c>
       <c r="D3" t="n">
-        <v>18103</v>
+        <v>20867</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2797</v>
+        <v>2297</v>
       </c>
       <c r="C4" t="n">
-        <v>4436</v>
+        <v>5063</v>
       </c>
       <c r="D4" t="n">
-        <v>9340</v>
+        <v>11646</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>1693</v>
       </c>
       <c r="C5" t="n">
-        <v>4474</v>
+        <v>5481</v>
       </c>
       <c r="D5" t="n">
-        <v>3811</v>
+        <v>5018</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1402</v>
+        <v>1133</v>
       </c>
       <c r="C6" t="n">
-        <v>3711</v>
+        <v>5020</v>
       </c>
       <c r="D6" t="n">
-        <v>1522</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>806</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>2479</v>
+        <v>3528</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>379</v>
+        <v>272</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>2075</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>1032</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>289</v>
+        <v>452</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9081</v>
+        <v>6028</v>
       </c>
       <c r="C2" t="n">
-        <v>4178</v>
+        <v>5936</v>
       </c>
       <c r="D2" t="n">
-        <v>28087</v>
+        <v>34388</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5257</v>
+        <v>4067</v>
       </c>
       <c r="C3" t="n">
-        <v>8158</v>
+        <v>8000</v>
       </c>
       <c r="D3" t="n">
-        <v>19739</v>
+        <v>22519</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1868</v>
+        <v>1564</v>
       </c>
       <c r="C4" t="n">
-        <v>6807</v>
+        <v>7886</v>
       </c>
       <c r="D4" t="n">
-        <v>8784</v>
+        <v>11007</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1295</v>
+        <v>1046</v>
       </c>
       <c r="C5" t="n">
-        <v>3636</v>
+        <v>4919</v>
       </c>
       <c r="D5" t="n">
-        <v>2552</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>561</v>
       </c>
       <c r="C6" t="n">
-        <v>2429</v>
+        <v>3457</v>
       </c>
       <c r="D6" t="n">
-        <v>780</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>1247</v>
+        <v>2033</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>550</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5417</v>
+        <v>3602</v>
       </c>
       <c r="C2" t="n">
-        <v>1895</v>
+        <v>2760</v>
       </c>
       <c r="D2" t="n">
-        <v>20209</v>
+        <v>24336</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5962</v>
+        <v>4188</v>
       </c>
       <c r="C3" t="n">
-        <v>5687</v>
+        <v>6474</v>
       </c>
       <c r="D3" t="n">
-        <v>19962</v>
+        <v>22777</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2745</v>
+        <v>2134</v>
       </c>
       <c r="C4" t="n">
-        <v>7575</v>
+        <v>8075</v>
       </c>
       <c r="D4" t="n">
-        <v>10368</v>
+        <v>12541</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1430</v>
+        <v>1166</v>
       </c>
       <c r="C5" t="n">
-        <v>5074</v>
+        <v>6144</v>
       </c>
       <c r="D5" t="n">
-        <v>3301</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>899</v>
+        <v>654</v>
       </c>
       <c r="C6" t="n">
-        <v>2981</v>
+        <v>4146</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>234</v>
       </c>
       <c r="C7" t="n">
-        <v>1692</v>
+        <v>2540</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>748</v>
+        <v>1323</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>463</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
+        <v>2868</v>
       </c>
       <c r="C2" t="n">
-        <v>3215</v>
+        <v>3761</v>
       </c>
       <c r="D2" t="n">
-        <v>20001</v>
+        <v>20489</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4802</v>
+        <v>3358</v>
       </c>
       <c r="C3" t="n">
-        <v>3369</v>
+        <v>4251</v>
       </c>
       <c r="D3" t="n">
-        <v>18624</v>
+        <v>21677</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3587</v>
+        <v>2537</v>
       </c>
       <c r="C4" t="n">
-        <v>6529</v>
+        <v>7153</v>
       </c>
       <c r="D4" t="n">
-        <v>11710</v>
+        <v>13611</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1767</v>
+        <v>1383</v>
       </c>
       <c r="C5" t="n">
-        <v>6168</v>
+        <v>6946</v>
       </c>
       <c r="D5" t="n">
-        <v>4353</v>
+        <v>5272</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>3944</v>
+        <v>4951</v>
       </c>
       <c r="D6" t="n">
-        <v>1309</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>2259</v>
+        <v>3224</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>1152</v>
+        <v>1800</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>770</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2819</v>
+        <v>1737</v>
       </c>
       <c r="C2" t="n">
-        <v>1468</v>
+        <v>1839</v>
       </c>
       <c r="D2" t="n">
-        <v>13816</v>
+        <v>14272</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4619</v>
+        <v>3137</v>
       </c>
       <c r="C3" t="n">
-        <v>3201</v>
+        <v>3978</v>
       </c>
       <c r="D3" t="n">
-        <v>18331</v>
+        <v>21067</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3980</v>
+        <v>2785</v>
       </c>
       <c r="C4" t="n">
-        <v>5990</v>
+        <v>6799</v>
       </c>
       <c r="D4" t="n">
-        <v>12579</v>
+        <v>14648</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1849</v>
+        <v>1416</v>
       </c>
       <c r="C5" t="n">
-        <v>7102</v>
+        <v>8181</v>
       </c>
       <c r="D5" t="n">
-        <v>4756</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>890</v>
+        <v>622</v>
       </c>
       <c r="C6" t="n">
-        <v>4811</v>
+        <v>5786</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>2283</v>
+        <v>3337</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>867</v>
+        <v>1266</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>2414</v>
       </c>
       <c r="C2" t="n">
-        <v>5971</v>
+        <v>5176</v>
       </c>
       <c r="D2" t="n">
-        <v>11128</v>
+        <v>13958</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3308</v>
+        <v>2199</v>
       </c>
       <c r="C3" t="n">
-        <v>2116</v>
+        <v>2730</v>
       </c>
       <c r="D3" t="n">
-        <v>16485</v>
+        <v>18815</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3710</v>
+        <v>2581</v>
       </c>
       <c r="C4" t="n">
-        <v>4557</v>
+        <v>5384</v>
       </c>
       <c r="D4" t="n">
-        <v>13135</v>
+        <v>15188</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>6510</v>
+        <v>7492</v>
       </c>
       <c r="D5" t="n">
-        <v>5813</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1155</v>
+        <v>817</v>
       </c>
       <c r="C6" t="n">
-        <v>5802</v>
+        <v>6757</v>
       </c>
       <c r="D6" t="n">
-        <v>1784</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>230</v>
       </c>
       <c r="C7" t="n">
-        <v>3367</v>
+        <v>4337</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1410</v>
+        <v>2000</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2598</v>
+        <v>1577</v>
       </c>
       <c r="C2" t="n">
-        <v>3469</v>
+        <v>3252</v>
       </c>
       <c r="D2" t="n">
-        <v>8376</v>
+        <v>10654</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3010</v>
+        <v>1986</v>
       </c>
       <c r="C3" t="n">
-        <v>3334</v>
+        <v>3326</v>
       </c>
       <c r="D3" t="n">
-        <v>14945</v>
+        <v>17277</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3304</v>
+        <v>2280</v>
       </c>
       <c r="C4" t="n">
-        <v>3562</v>
+        <v>4382</v>
       </c>
       <c r="D4" t="n">
-        <v>13312</v>
+        <v>15324</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2664</v>
+        <v>1877</v>
       </c>
       <c r="C5" t="n">
-        <v>5893</v>
+        <v>6895</v>
       </c>
       <c r="D5" t="n">
-        <v>6591</v>
+        <v>7494</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1378</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>6269</v>
+        <v>7256</v>
       </c>
       <c r="D6" t="n">
-        <v>2145</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>4217</v>
+        <v>5178</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>1873</v>
+        <v>2531</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>661</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4884</v>
+        <v>1838</v>
       </c>
       <c r="C2" t="n">
-        <v>7487</v>
+        <v>10680</v>
       </c>
       <c r="D2" t="n">
-        <v>14425</v>
+        <v>10105</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2405</v>
+        <v>1554</v>
       </c>
       <c r="C3" t="n">
-        <v>3004</v>
+        <v>2938</v>
       </c>
       <c r="D3" t="n">
-        <v>13267</v>
+        <v>15542</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2778</v>
+        <v>1913</v>
       </c>
       <c r="C4" t="n">
-        <v>3387</v>
+        <v>3854</v>
       </c>
       <c r="D4" t="n">
-        <v>13014</v>
+        <v>14973</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2659</v>
+        <v>1835</v>
       </c>
       <c r="C5" t="n">
-        <v>4785</v>
+        <v>5762</v>
       </c>
       <c r="D5" t="n">
-        <v>7358</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1678</v>
+        <v>1160</v>
       </c>
       <c r="C6" t="n">
-        <v>6062</v>
+        <v>7061</v>
       </c>
       <c r="D6" t="n">
-        <v>2714</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>5061</v>
+        <v>5929</v>
       </c>
       <c r="D7" t="n">
-        <v>924</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>2722</v>
+        <v>3462</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1022</v>
+        <v>1253</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5109</v>
+        <v>4452</v>
       </c>
       <c r="C2" t="n">
-        <v>2699</v>
+        <v>12470</v>
       </c>
       <c r="D2" t="n">
-        <v>9546</v>
+        <v>15570</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3456</v>
+        <v>1329</v>
       </c>
       <c r="C2" t="n">
-        <v>4192</v>
+        <v>6237</v>
       </c>
       <c r="D2" t="n">
-        <v>10616</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3369</v>
+        <v>2090</v>
       </c>
       <c r="C3" t="n">
-        <v>4334</v>
+        <v>4873</v>
       </c>
       <c r="D3" t="n">
-        <v>14409</v>
+        <v>16492</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3873</v>
+        <v>2672</v>
       </c>
       <c r="C4" t="n">
-        <v>5021</v>
+        <v>5779</v>
       </c>
       <c r="D4" t="n">
-        <v>13439</v>
+        <v>15364</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1648</v>
+        <v>1105</v>
       </c>
       <c r="C5" t="n">
-        <v>7803</v>
+        <v>9311</v>
       </c>
       <c r="D5" t="n">
-        <v>6698</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>561</v>
+        <v>352</v>
       </c>
       <c r="C6" t="n">
-        <v>6266</v>
+        <v>7125</v>
       </c>
       <c r="D6" t="n">
-        <v>2108</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2667</v>
+        <v>3392</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1001</v>
+        <v>1227</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7136</v>
+        <v>5953</v>
       </c>
       <c r="C2" t="n">
-        <v>4224</v>
+        <v>8402</v>
       </c>
       <c r="D2" t="n">
-        <v>13260</v>
+        <v>25949</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2171</v>
+        <v>1893</v>
       </c>
       <c r="C3" t="n">
-        <v>1381</v>
+        <v>6284</v>
       </c>
       <c r="D3" t="n">
-        <v>2319</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4444</v>
+        <v>3840</v>
       </c>
       <c r="C2" t="n">
-        <v>3290</v>
+        <v>4750</v>
       </c>
       <c r="D2" t="n">
-        <v>16569</v>
+        <v>34541</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3817</v>
+        <v>3219</v>
       </c>
       <c r="C3" t="n">
-        <v>2598</v>
+        <v>6452</v>
       </c>
       <c r="D3" t="n">
-        <v>3986</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>976</v>
+        <v>856</v>
       </c>
       <c r="C4" t="n">
-        <v>865</v>
+        <v>3725</v>
       </c>
       <c r="D4" t="n">
-        <v>1648</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4980,10 +4980,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4791</v>
+        <v>4558</v>
       </c>
       <c r="C2" t="n">
-        <v>9910</v>
+        <v>9209</v>
       </c>
       <c r="D2" t="n">
-        <v>15911</v>
+        <v>39705</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3403</v>
+        <v>2900</v>
       </c>
       <c r="C3" t="n">
-        <v>2576</v>
+        <v>4805</v>
       </c>
       <c r="D3" t="n">
-        <v>5712</v>
+        <v>10770</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>1702</v>
       </c>
       <c r="C4" t="n">
-        <v>1845</v>
+        <v>5165</v>
       </c>
       <c r="D4" t="n">
-        <v>2030</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>574</v>
+        <v>2101</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5248</v>
+        <v>5364</v>
       </c>
       <c r="C2" t="n">
-        <v>6437</v>
+        <v>11719</v>
       </c>
       <c r="D2" t="n">
-        <v>23571</v>
+        <v>30288</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3347</v>
+        <v>2999</v>
       </c>
       <c r="C3" t="n">
-        <v>5582</v>
+        <v>6173</v>
       </c>
       <c r="D3" t="n">
-        <v>6860</v>
+        <v>14195</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2338</v>
+        <v>1923</v>
       </c>
       <c r="C4" t="n">
-        <v>2206</v>
+        <v>4821</v>
       </c>
       <c r="D4" t="n">
-        <v>2620</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1040</v>
+        <v>852</v>
       </c>
       <c r="C5" t="n">
-        <v>1227</v>
+        <v>3616</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>440</v>
+        <v>1178</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6280</v>
+        <v>5738</v>
       </c>
       <c r="C2" t="n">
-        <v>8311</v>
+        <v>10788</v>
       </c>
       <c r="D2" t="n">
-        <v>31241</v>
+        <v>28982</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3121</v>
+        <v>2987</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>7298</v>
       </c>
       <c r="D3" t="n">
-        <v>8388</v>
+        <v>14603</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1763</v>
+        <v>1517</v>
       </c>
       <c r="C4" t="n">
-        <v>3346</v>
+        <v>4490</v>
       </c>
       <c r="D4" t="n">
-        <v>2868</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>893</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
-        <v>1283</v>
+        <v>3080</v>
       </c>
       <c r="D5" t="n">
-        <v>1245</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>566</v>
+        <v>1580</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>254</v>
+        <v>478</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5384</v>
+        <v>4343</v>
       </c>
       <c r="C2" t="n">
-        <v>4760</v>
+        <v>5479</v>
       </c>
       <c r="D2" t="n">
-        <v>33600</v>
+        <v>39591</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3936</v>
+        <v>3588</v>
       </c>
       <c r="C3" t="n">
-        <v>5979</v>
+        <v>7996</v>
       </c>
       <c r="D3" t="n">
-        <v>11779</v>
+        <v>15943</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2156</v>
+        <v>1957</v>
       </c>
       <c r="C4" t="n">
-        <v>4267</v>
+        <v>6040</v>
       </c>
       <c r="D4" t="n">
-        <v>3946</v>
+        <v>6703</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>974</v>
       </c>
       <c r="C5" t="n">
-        <v>2504</v>
+        <v>3814</v>
       </c>
       <c r="D5" t="n">
-        <v>1522</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>566</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>978</v>
+        <v>2366</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>434</v>
+        <v>1082</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4997</v>
+        <v>4454</v>
       </c>
       <c r="C2" t="n">
-        <v>7153</v>
+        <v>5239</v>
       </c>
       <c r="D2" t="n">
-        <v>30970</v>
+        <v>36101</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3873</v>
+        <v>3253</v>
       </c>
       <c r="C3" t="n">
-        <v>4561</v>
+        <v>5832</v>
       </c>
       <c r="D3" t="n">
-        <v>14577</v>
+        <v>18415</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>2353</v>
       </c>
       <c r="C4" t="n">
-        <v>5180</v>
+        <v>6965</v>
       </c>
       <c r="D4" t="n">
-        <v>5405</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1480</v>
+        <v>1254</v>
       </c>
       <c r="C5" t="n">
-        <v>3450</v>
+        <v>4852</v>
       </c>
       <c r="D5" t="n">
-        <v>1941</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>797</v>
+        <v>632</v>
       </c>
       <c r="C6" t="n">
-        <v>1801</v>
+        <v>3076</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>727</v>
+        <v>1723</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>337</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_38_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5688</v>
+        <v>5072</v>
       </c>
       <c r="C2" t="n">
-        <v>6347</v>
+        <v>9464</v>
       </c>
       <c r="D2" t="n">
-        <v>36220</v>
+        <v>18925</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3111</v>
+        <v>3272</v>
       </c>
       <c r="C3" t="n">
-        <v>4880</v>
+        <v>6043</v>
       </c>
       <c r="D3" t="n">
-        <v>19582</v>
+        <v>11467</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2374</v>
+        <v>2495</v>
       </c>
       <c r="C4" t="n">
-        <v>6198</v>
+        <v>6532</v>
       </c>
       <c r="D4" t="n">
-        <v>9526</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1517</v>
+        <v>1588</v>
       </c>
       <c r="C5" t="n">
-        <v>5765</v>
+        <v>4727</v>
       </c>
       <c r="D5" t="n">
-        <v>3617</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>3833</v>
+        <v>2701</v>
       </c>
       <c r="D6" t="n">
-        <v>1333</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>471</v>
       </c>
       <c r="C7" t="n">
-        <v>2345</v>
+        <v>1626</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>1144</v>
+        <v>868</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>404</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5579</v>
+        <v>7565</v>
       </c>
       <c r="C2" t="n">
-        <v>7297</v>
+        <v>10677</v>
       </c>
       <c r="D2" t="n">
-        <v>35739</v>
+        <v>16908</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>3333</v>
       </c>
       <c r="C3" t="n">
-        <v>4869</v>
+        <v>6703</v>
       </c>
       <c r="D3" t="n">
-        <v>20427</v>
+        <v>11710</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>2452</v>
       </c>
       <c r="C4" t="n">
-        <v>5474</v>
+        <v>6094</v>
       </c>
       <c r="D4" t="n">
-        <v>10781</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1665</v>
+        <v>1751</v>
       </c>
       <c r="C5" t="n">
-        <v>5776</v>
+        <v>5495</v>
       </c>
       <c r="D5" t="n">
-        <v>4323</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>1123</v>
       </c>
       <c r="C6" t="n">
-        <v>4613</v>
+        <v>3581</v>
       </c>
       <c r="D6" t="n">
-        <v>1644</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>617</v>
       </c>
       <c r="C7" t="n">
-        <v>2933</v>
+        <v>2120</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="C8" t="n">
-        <v>1614</v>
+        <v>1193</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>727</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6502</v>
+        <v>9062</v>
       </c>
       <c r="C2" t="n">
-        <v>8433</v>
+        <v>15887</v>
       </c>
       <c r="D2" t="n">
-        <v>41483</v>
+        <v>21584</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3440</v>
+        <v>4092</v>
       </c>
       <c r="C3" t="n">
-        <v>5162</v>
+        <v>7425</v>
       </c>
       <c r="D3" t="n">
-        <v>20867</v>
+        <v>11607</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2297</v>
+        <v>2402</v>
       </c>
       <c r="C4" t="n">
-        <v>5063</v>
+        <v>6242</v>
       </c>
       <c r="D4" t="n">
-        <v>11646</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1693</v>
+        <v>1813</v>
       </c>
       <c r="C5" t="n">
-        <v>5481</v>
+        <v>5586</v>
       </c>
       <c r="D5" t="n">
-        <v>5018</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1133</v>
+        <v>1273</v>
       </c>
       <c r="C6" t="n">
-        <v>5020</v>
+        <v>4321</v>
       </c>
       <c r="D6" t="n">
-        <v>1982</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>739</v>
       </c>
       <c r="C7" t="n">
-        <v>3528</v>
+        <v>2734</v>
       </c>
       <c r="D7" t="n">
-        <v>848</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="C8" t="n">
-        <v>2075</v>
+        <v>1553</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="C9" t="n">
-        <v>1032</v>
+        <v>834</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6028</v>
+        <v>8130</v>
       </c>
       <c r="C2" t="n">
-        <v>5936</v>
+        <v>10676</v>
       </c>
       <c r="D2" t="n">
-        <v>34388</v>
+        <v>17712</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4067</v>
+        <v>4661</v>
       </c>
       <c r="C3" t="n">
-        <v>8000</v>
+        <v>11618</v>
       </c>
       <c r="D3" t="n">
-        <v>22519</v>
+        <v>12655</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1564</v>
+        <v>1675</v>
       </c>
       <c r="C4" t="n">
-        <v>7886</v>
+        <v>8898</v>
       </c>
       <c r="D4" t="n">
-        <v>11007</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1046</v>
+        <v>1176</v>
       </c>
       <c r="C5" t="n">
-        <v>4919</v>
+        <v>4234</v>
       </c>
       <c r="D5" t="n">
-        <v>3243</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>561</v>
+        <v>682</v>
       </c>
       <c r="C6" t="n">
-        <v>3457</v>
+        <v>2679</v>
       </c>
       <c r="D6" t="n">
-        <v>831</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>2033</v>
+        <v>1521</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>817</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3602</v>
+        <v>4776</v>
       </c>
       <c r="C2" t="n">
-        <v>2760</v>
+        <v>5137</v>
       </c>
       <c r="D2" t="n">
-        <v>24336</v>
+        <v>12417</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4188</v>
+        <v>5247</v>
       </c>
       <c r="C3" t="n">
-        <v>6474</v>
+        <v>10129</v>
       </c>
       <c r="D3" t="n">
-        <v>22777</v>
+        <v>12613</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2134</v>
+        <v>2445</v>
       </c>
       <c r="C4" t="n">
-        <v>8075</v>
+        <v>10248</v>
       </c>
       <c r="D4" t="n">
-        <v>12541</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1166</v>
+        <v>1305</v>
       </c>
       <c r="C5" t="n">
-        <v>6144</v>
+        <v>6319</v>
       </c>
       <c r="D5" t="n">
-        <v>4101</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>654</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>4146</v>
+        <v>3394</v>
       </c>
       <c r="D6" t="n">
-        <v>1053</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>2540</v>
+        <v>1957</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>1323</v>
+        <v>1064</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2868</v>
+        <v>5204</v>
       </c>
       <c r="C2" t="n">
-        <v>3761</v>
+        <v>7266</v>
       </c>
       <c r="D2" t="n">
-        <v>20489</v>
+        <v>15371</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3358</v>
+        <v>4235</v>
       </c>
       <c r="C3" t="n">
-        <v>4251</v>
+        <v>6845</v>
       </c>
       <c r="D3" t="n">
-        <v>21677</v>
+        <v>11838</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2537</v>
+        <v>3148</v>
       </c>
       <c r="C4" t="n">
-        <v>7153</v>
+        <v>9975</v>
       </c>
       <c r="D4" t="n">
-        <v>13611</v>
+        <v>7776</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1383</v>
+        <v>1584</v>
       </c>
       <c r="C5" t="n">
-        <v>6946</v>
+        <v>8134</v>
       </c>
       <c r="D5" t="n">
-        <v>5272</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>939</v>
       </c>
       <c r="C6" t="n">
-        <v>4951</v>
+        <v>4680</v>
       </c>
       <c r="D6" t="n">
-        <v>1478</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="C7" t="n">
-        <v>3224</v>
+        <v>2609</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>1800</v>
+        <v>1441</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>770</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1737</v>
+        <v>3063</v>
       </c>
       <c r="C2" t="n">
-        <v>1839</v>
+        <v>3391</v>
       </c>
       <c r="D2" t="n">
-        <v>14272</v>
+        <v>10719</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3137</v>
+        <v>4310</v>
       </c>
       <c r="C3" t="n">
-        <v>3978</v>
+        <v>6712</v>
       </c>
       <c r="D3" t="n">
-        <v>21067</v>
+        <v>11940</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>3479</v>
       </c>
       <c r="C4" t="n">
-        <v>6799</v>
+        <v>9769</v>
       </c>
       <c r="D4" t="n">
-        <v>14648</v>
+        <v>8294</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1656</v>
       </c>
       <c r="C5" t="n">
-        <v>8181</v>
+        <v>9676</v>
       </c>
       <c r="D5" t="n">
-        <v>5525</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>622</v>
+        <v>802</v>
       </c>
       <c r="C6" t="n">
-        <v>5786</v>
+        <v>5643</v>
       </c>
       <c r="D6" t="n">
-        <v>1418</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>3337</v>
+        <v>2698</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1266</v>
+        <v>1128</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2414</v>
+        <v>3440</v>
       </c>
       <c r="C2" t="n">
-        <v>5176</v>
+        <v>3373</v>
       </c>
       <c r="D2" t="n">
-        <v>13958</v>
+        <v>13578</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2199</v>
+        <v>3244</v>
       </c>
       <c r="C3" t="n">
-        <v>2730</v>
+        <v>4642</v>
       </c>
       <c r="D3" t="n">
-        <v>18815</v>
+        <v>10971</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2581</v>
+        <v>3329</v>
       </c>
       <c r="C4" t="n">
-        <v>5384</v>
+        <v>8127</v>
       </c>
       <c r="D4" t="n">
-        <v>15188</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>2107</v>
       </c>
       <c r="C5" t="n">
-        <v>7492</v>
+        <v>9609</v>
       </c>
       <c r="D5" t="n">
-        <v>6670</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>817</v>
+        <v>1030</v>
       </c>
       <c r="C6" t="n">
-        <v>6757</v>
+        <v>7349</v>
       </c>
       <c r="D6" t="n">
-        <v>1965</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>4337</v>
+        <v>3933</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2000</v>
+        <v>1718</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1577</v>
+        <v>2474</v>
       </c>
       <c r="C2" t="n">
-        <v>3252</v>
+        <v>2804</v>
       </c>
       <c r="D2" t="n">
-        <v>10654</v>
+        <v>10536</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1986</v>
+        <v>2897</v>
       </c>
       <c r="C3" t="n">
-        <v>3326</v>
+        <v>3798</v>
       </c>
       <c r="D3" t="n">
-        <v>17277</v>
+        <v>10687</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2280</v>
+        <v>3041</v>
       </c>
       <c r="C4" t="n">
-        <v>4382</v>
+        <v>6786</v>
       </c>
       <c r="D4" t="n">
-        <v>15324</v>
+        <v>8921</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1877</v>
+        <v>2317</v>
       </c>
       <c r="C5" t="n">
-        <v>6895</v>
+        <v>9159</v>
       </c>
       <c r="D5" t="n">
-        <v>7494</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1227</v>
       </c>
       <c r="C6" t="n">
-        <v>7256</v>
+        <v>8353</v>
       </c>
       <c r="D6" t="n">
-        <v>2341</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>5178</v>
+        <v>5038</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2531</v>
+        <v>2244</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1838</v>
+        <v>3449</v>
       </c>
       <c r="C2" t="n">
-        <v>10680</v>
+        <v>6644</v>
       </c>
       <c r="D2" t="n">
-        <v>10105</v>
+        <v>11294</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1554</v>
+        <v>2292</v>
       </c>
       <c r="C3" t="n">
-        <v>2938</v>
+        <v>3028</v>
       </c>
       <c r="D3" t="n">
-        <v>15542</v>
+        <v>9984</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1913</v>
+        <v>2624</v>
       </c>
       <c r="C4" t="n">
-        <v>3854</v>
+        <v>5382</v>
       </c>
       <c r="D4" t="n">
-        <v>14973</v>
+        <v>8904</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1835</v>
+        <v>2332</v>
       </c>
       <c r="C5" t="n">
-        <v>5762</v>
+        <v>8011</v>
       </c>
       <c r="D5" t="n">
-        <v>8318</v>
+        <v>4889</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1160</v>
+        <v>1479</v>
       </c>
       <c r="C6" t="n">
-        <v>7061</v>
+        <v>8592</v>
       </c>
       <c r="D6" t="n">
-        <v>2954</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>511</v>
       </c>
       <c r="C7" t="n">
-        <v>5929</v>
+        <v>6319</v>
       </c>
       <c r="D7" t="n">
-        <v>939</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>3462</v>
+        <v>3201</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1253</v>
+        <v>1190</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4452</v>
+        <v>5615</v>
       </c>
       <c r="C2" t="n">
-        <v>12470</v>
+        <v>8077</v>
       </c>
       <c r="D2" t="n">
-        <v>15570</v>
+        <v>7489</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1329</v>
+        <v>2495</v>
       </c>
       <c r="C2" t="n">
-        <v>6237</v>
+        <v>3826</v>
       </c>
       <c r="D2" t="n">
-        <v>7518</v>
+        <v>8402</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2090</v>
+        <v>3078</v>
       </c>
       <c r="C3" t="n">
-        <v>4873</v>
+        <v>4104</v>
       </c>
       <c r="D3" t="n">
-        <v>16492</v>
+        <v>10815</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2672</v>
+        <v>3497</v>
       </c>
       <c r="C4" t="n">
-        <v>5779</v>
+        <v>7995</v>
       </c>
       <c r="D4" t="n">
-        <v>15364</v>
+        <v>9122</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1105</v>
+        <v>1409</v>
       </c>
       <c r="C5" t="n">
-        <v>9311</v>
+        <v>11973</v>
       </c>
       <c r="D5" t="n">
-        <v>7465</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>352</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>7125</v>
+        <v>7792</v>
       </c>
       <c r="D6" t="n">
-        <v>2219</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>3392</v>
+        <v>3136</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1227</v>
+        <v>1166</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5953</v>
+        <v>6399</v>
       </c>
       <c r="C2" t="n">
-        <v>8402</v>
+        <v>4505</v>
       </c>
       <c r="D2" t="n">
-        <v>25949</v>
+        <v>9645</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1893</v>
+        <v>2386</v>
       </c>
       <c r="C3" t="n">
-        <v>6284</v>
+        <v>4070</v>
       </c>
       <c r="D3" t="n">
-        <v>3255</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3840</v>
+        <v>4234</v>
       </c>
       <c r="C2" t="n">
-        <v>4750</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
-        <v>34541</v>
+        <v>10345</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3219</v>
+        <v>3606</v>
       </c>
       <c r="C3" t="n">
-        <v>6452</v>
+        <v>3719</v>
       </c>
       <c r="D3" t="n">
-        <v>6828</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>856</v>
+        <v>1070</v>
       </c>
       <c r="C4" t="n">
-        <v>3725</v>
+        <v>2466</v>
       </c>
       <c r="D4" t="n">
-        <v>1837</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,10 +4980,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4558</v>
+        <v>4219</v>
       </c>
       <c r="C2" t="n">
-        <v>9209</v>
+        <v>5930</v>
       </c>
       <c r="D2" t="n">
-        <v>39705</v>
+        <v>9181</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2900</v>
+        <v>3226</v>
       </c>
       <c r="C3" t="n">
-        <v>4805</v>
+        <v>3036</v>
       </c>
       <c r="D3" t="n">
-        <v>10770</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1702</v>
+        <v>1979</v>
       </c>
       <c r="C4" t="n">
-        <v>5165</v>
+        <v>3100</v>
       </c>
       <c r="D4" t="n">
-        <v>2739</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>407</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>2101</v>
+        <v>1465</v>
       </c>
       <c r="D5" t="n">
-        <v>1278</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5364</v>
+        <v>4515</v>
       </c>
       <c r="C2" t="n">
-        <v>11719</v>
+        <v>8575</v>
       </c>
       <c r="D2" t="n">
-        <v>30288</v>
+        <v>25015</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2999</v>
+        <v>3043</v>
       </c>
       <c r="C3" t="n">
-        <v>6173</v>
+        <v>3957</v>
       </c>
       <c r="D3" t="n">
-        <v>14195</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1923</v>
+        <v>2202</v>
       </c>
       <c r="C4" t="n">
-        <v>4821</v>
+        <v>3000</v>
       </c>
       <c r="D4" t="n">
-        <v>4017</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>852</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="n">
-        <v>3616</v>
+        <v>2297</v>
       </c>
       <c r="D5" t="n">
-        <v>1491</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>1178</v>
+        <v>887</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5738</v>
+        <v>5563</v>
       </c>
       <c r="C2" t="n">
-        <v>10788</v>
+        <v>11238</v>
       </c>
       <c r="D2" t="n">
-        <v>28982</v>
+        <v>20724</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2987</v>
+        <v>2747</v>
       </c>
       <c r="C3" t="n">
-        <v>7298</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>14603</v>
+        <v>6874</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1517</v>
+        <v>1639</v>
       </c>
       <c r="C4" t="n">
-        <v>4490</v>
+        <v>2900</v>
       </c>
       <c r="D4" t="n">
-        <v>4895</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>710</v>
+        <v>845</v>
       </c>
       <c r="C5" t="n">
-        <v>3080</v>
+        <v>1931</v>
       </c>
       <c r="D5" t="n">
-        <v>1524</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>1580</v>
+        <v>1086</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>478</v>
+        <v>396</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4343</v>
+        <v>5275</v>
       </c>
       <c r="C2" t="n">
-        <v>5479</v>
+        <v>8877</v>
       </c>
       <c r="D2" t="n">
-        <v>39591</v>
+        <v>19834</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3588</v>
+        <v>3479</v>
       </c>
       <c r="C3" t="n">
-        <v>7996</v>
+        <v>7593</v>
       </c>
       <c r="D3" t="n">
-        <v>15943</v>
+        <v>8794</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1957</v>
+        <v>1934</v>
       </c>
       <c r="C4" t="n">
-        <v>6040</v>
+        <v>4279</v>
       </c>
       <c r="D4" t="n">
-        <v>6703</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>974</v>
+        <v>1108</v>
       </c>
       <c r="C5" t="n">
-        <v>3814</v>
+        <v>2476</v>
       </c>
       <c r="D5" t="n">
-        <v>2124</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>441</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>2366</v>
+        <v>1567</v>
       </c>
       <c r="D6" t="n">
-        <v>892</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>1082</v>
+        <v>794</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>196</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4454</v>
+        <v>4307</v>
       </c>
       <c r="C2" t="n">
-        <v>5239</v>
+        <v>6724</v>
       </c>
       <c r="D2" t="n">
-        <v>36101</v>
+        <v>24660</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>3592</v>
       </c>
       <c r="C3" t="n">
-        <v>5832</v>
+        <v>7176</v>
       </c>
       <c r="D3" t="n">
-        <v>18415</v>
+        <v>9927</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2353</v>
+        <v>2322</v>
       </c>
       <c r="C4" t="n">
-        <v>6965</v>
+        <v>6057</v>
       </c>
       <c r="D4" t="n">
-        <v>8184</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1254</v>
+        <v>1350</v>
       </c>
       <c r="C5" t="n">
-        <v>4852</v>
+        <v>3445</v>
       </c>
       <c r="D5" t="n">
-        <v>2830</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>632</v>
+        <v>753</v>
       </c>
       <c r="C6" t="n">
-        <v>3076</v>
+        <v>2045</v>
       </c>
       <c r="D6" t="n">
-        <v>1092</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1723</v>
+        <v>1210</v>
       </c>
       <c r="D7" t="n">
         <v>604</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>701</v>
+        <v>565</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_38_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5072</v>
+        <v>1137</v>
       </c>
       <c r="C2" t="n">
-        <v>9464</v>
+        <v>4101</v>
       </c>
       <c r="D2" t="n">
-        <v>18925</v>
+        <v>19912</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3272</v>
+        <v>2226</v>
       </c>
       <c r="C3" t="n">
-        <v>6043</v>
+        <v>9800</v>
       </c>
       <c r="D3" t="n">
-        <v>11467</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>1610</v>
       </c>
       <c r="C4" t="n">
-        <v>6532</v>
+        <v>9696</v>
       </c>
       <c r="D4" t="n">
-        <v>5007</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1588</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>4727</v>
+        <v>5183</v>
       </c>
       <c r="D5" t="n">
-        <v>1958</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>2701</v>
+        <v>2229</v>
       </c>
       <c r="D6" t="n">
-        <v>994</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>471</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>1626</v>
+        <v>789</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>868</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7565</v>
+        <v>1226</v>
       </c>
       <c r="C2" t="n">
-        <v>10677</v>
+        <v>6841</v>
       </c>
       <c r="D2" t="n">
-        <v>16908</v>
+        <v>18757</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>1461</v>
       </c>
       <c r="C3" t="n">
-        <v>6703</v>
+        <v>6070</v>
       </c>
       <c r="D3" t="n">
-        <v>11710</v>
+        <v>15421</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2452</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="n">
-        <v>6094</v>
+        <v>9549</v>
       </c>
       <c r="D4" t="n">
-        <v>5860</v>
+        <v>7721</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1751</v>
+        <v>1036</v>
       </c>
       <c r="C5" t="n">
-        <v>5495</v>
+        <v>7421</v>
       </c>
       <c r="D5" t="n">
-        <v>2396</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1123</v>
+        <v>490</v>
       </c>
       <c r="C6" t="n">
-        <v>3581</v>
+        <v>3645</v>
       </c>
       <c r="D6" t="n">
-        <v>1119</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>617</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>2120</v>
+        <v>1459</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1193</v>
+        <v>547</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9062</v>
+        <v>671</v>
       </c>
       <c r="C2" t="n">
-        <v>15887</v>
+        <v>2990</v>
       </c>
       <c r="D2" t="n">
-        <v>21584</v>
+        <v>12804</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>1347</v>
       </c>
       <c r="C3" t="n">
-        <v>7425</v>
+        <v>6072</v>
       </c>
       <c r="D3" t="n">
-        <v>11607</v>
+        <v>15426</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2402</v>
+        <v>1779</v>
       </c>
       <c r="C4" t="n">
-        <v>6242</v>
+        <v>9056</v>
       </c>
       <c r="D4" t="n">
-        <v>6580</v>
+        <v>8670</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1813</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="n">
-        <v>5586</v>
+        <v>8937</v>
       </c>
       <c r="D5" t="n">
-        <v>2798</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1273</v>
+        <v>370</v>
       </c>
       <c r="C6" t="n">
-        <v>4321</v>
+        <v>4556</v>
       </c>
       <c r="D6" t="n">
-        <v>1288</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>739</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2734</v>
+        <v>1368</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>361</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1553</v>
+        <v>489</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>834</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>406</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8130</v>
+        <v>794</v>
       </c>
       <c r="C2" t="n">
-        <v>10676</v>
+        <v>6713</v>
       </c>
       <c r="D2" t="n">
-        <v>17712</v>
+        <v>13208</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4661</v>
+        <v>901</v>
       </c>
       <c r="C3" t="n">
-        <v>11618</v>
+        <v>4031</v>
       </c>
       <c r="D3" t="n">
-        <v>12655</v>
+        <v>13987</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1675</v>
+        <v>1421</v>
       </c>
       <c r="C4" t="n">
-        <v>8898</v>
+        <v>7436</v>
       </c>
       <c r="D4" t="n">
-        <v>6265</v>
+        <v>9657</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1176</v>
+        <v>1206</v>
       </c>
       <c r="C5" t="n">
-        <v>4234</v>
+        <v>8894</v>
       </c>
       <c r="D5" t="n">
-        <v>2041</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>682</v>
+        <v>567</v>
       </c>
       <c r="C6" t="n">
-        <v>2679</v>
+        <v>6577</v>
       </c>
       <c r="D6" t="n">
-        <v>717</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>2737</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4776</v>
+        <v>470</v>
       </c>
       <c r="C2" t="n">
-        <v>5137</v>
+        <v>3949</v>
       </c>
       <c r="D2" t="n">
-        <v>12417</v>
+        <v>9163</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5247</v>
+        <v>755</v>
       </c>
       <c r="C3" t="n">
-        <v>10129</v>
+        <v>4667</v>
       </c>
       <c r="D3" t="n">
-        <v>12613</v>
+        <v>13104</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2445</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>10248</v>
+        <v>5991</v>
       </c>
       <c r="D4" t="n">
-        <v>7176</v>
+        <v>10079</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1305</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>6319</v>
+        <v>8476</v>
       </c>
       <c r="D5" t="n">
-        <v>2545</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>683</v>
       </c>
       <c r="C6" t="n">
-        <v>3394</v>
+        <v>7629</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>1957</v>
+        <v>4004</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1064</v>
+        <v>1249</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5204</v>
+        <v>798</v>
       </c>
       <c r="C2" t="n">
-        <v>7266</v>
+        <v>8527</v>
       </c>
       <c r="D2" t="n">
-        <v>15371</v>
+        <v>14648</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4235</v>
+        <v>542</v>
       </c>
       <c r="C3" t="n">
-        <v>6845</v>
+        <v>3890</v>
       </c>
       <c r="D3" t="n">
-        <v>11838</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3148</v>
+        <v>883</v>
       </c>
       <c r="C4" t="n">
-        <v>9975</v>
+        <v>5268</v>
       </c>
       <c r="D4" t="n">
-        <v>7776</v>
+        <v>10237</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1584</v>
+        <v>1129</v>
       </c>
       <c r="C5" t="n">
-        <v>8134</v>
+        <v>7226</v>
       </c>
       <c r="D5" t="n">
-        <v>3223</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>939</v>
+        <v>822</v>
       </c>
       <c r="C6" t="n">
-        <v>4680</v>
+        <v>7909</v>
       </c>
       <c r="D6" t="n">
-        <v>1103</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>455</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>2609</v>
+        <v>5498</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1441</v>
+        <v>2286</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3063</v>
+        <v>555</v>
       </c>
       <c r="C2" t="n">
-        <v>3391</v>
+        <v>4638</v>
       </c>
       <c r="D2" t="n">
-        <v>10719</v>
+        <v>10663</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4310</v>
+        <v>808</v>
       </c>
       <c r="C3" t="n">
-        <v>6712</v>
+        <v>5394</v>
       </c>
       <c r="D3" t="n">
-        <v>11940</v>
+        <v>12913</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3479</v>
+        <v>1480</v>
       </c>
       <c r="C4" t="n">
-        <v>9769</v>
+        <v>7661</v>
       </c>
       <c r="D4" t="n">
-        <v>8294</v>
+        <v>10405</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1656</v>
+        <v>811</v>
       </c>
       <c r="C5" t="n">
-        <v>9676</v>
+        <v>10901</v>
       </c>
       <c r="D5" t="n">
-        <v>3405</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>802</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>5643</v>
+        <v>7093</v>
       </c>
       <c r="D6" t="n">
-        <v>1099</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>2698</v>
+        <v>2240</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1128</v>
+        <v>687</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3440</v>
+        <v>291</v>
       </c>
       <c r="C2" t="n">
-        <v>3373</v>
+        <v>2189</v>
       </c>
       <c r="D2" t="n">
-        <v>13578</v>
+        <v>8439</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3244</v>
+        <v>595</v>
       </c>
       <c r="C3" t="n">
-        <v>4642</v>
+        <v>4501</v>
       </c>
       <c r="D3" t="n">
-        <v>10971</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3329</v>
+        <v>988</v>
       </c>
       <c r="C4" t="n">
-        <v>8127</v>
+        <v>6151</v>
       </c>
       <c r="D4" t="n">
-        <v>8716</v>
+        <v>10059</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2107</v>
+        <v>766</v>
       </c>
       <c r="C5" t="n">
-        <v>9609</v>
+        <v>8367</v>
       </c>
       <c r="D5" t="n">
-        <v>4005</v>
+        <v>4787</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1030</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>7349</v>
+        <v>7074</v>
       </c>
       <c r="D6" t="n">
-        <v>1394</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>3933</v>
+        <v>3009</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1718</v>
+        <v>808</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>584</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2474</v>
+        <v>484</v>
       </c>
       <c r="C2" t="n">
-        <v>2804</v>
+        <v>4914</v>
       </c>
       <c r="D2" t="n">
-        <v>10536</v>
+        <v>8717</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2897</v>
+        <v>383</v>
       </c>
       <c r="C3" t="n">
-        <v>3798</v>
+        <v>2881</v>
       </c>
       <c r="D3" t="n">
-        <v>10687</v>
+        <v>10380</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3041</v>
+        <v>713</v>
       </c>
       <c r="C4" t="n">
-        <v>6786</v>
+        <v>5136</v>
       </c>
       <c r="D4" t="n">
-        <v>8921</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2317</v>
+        <v>786</v>
       </c>
       <c r="C5" t="n">
-        <v>9159</v>
+        <v>7124</v>
       </c>
       <c r="D5" t="n">
-        <v>4419</v>
+        <v>5552</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1227</v>
+        <v>438</v>
       </c>
       <c r="C6" t="n">
-        <v>8353</v>
+        <v>7632</v>
       </c>
       <c r="D6" t="n">
-        <v>1643</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>5038</v>
+        <v>4989</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2244</v>
+        <v>1807</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>677</v>
+        <v>491</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3449</v>
+        <v>791</v>
       </c>
       <c r="C2" t="n">
-        <v>6644</v>
+        <v>6761</v>
       </c>
       <c r="D2" t="n">
-        <v>11294</v>
+        <v>17520</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2292</v>
+        <v>351</v>
       </c>
       <c r="C3" t="n">
-        <v>3028</v>
+        <v>3360</v>
       </c>
       <c r="D3" t="n">
-        <v>9984</v>
+        <v>9456</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2624</v>
+        <v>501</v>
       </c>
       <c r="C4" t="n">
-        <v>5382</v>
+        <v>3925</v>
       </c>
       <c r="D4" t="n">
-        <v>8904</v>
+        <v>9703</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2332</v>
+        <v>686</v>
       </c>
       <c r="C5" t="n">
-        <v>8011</v>
+        <v>6040</v>
       </c>
       <c r="D5" t="n">
-        <v>4889</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1479</v>
+        <v>538</v>
       </c>
       <c r="C6" t="n">
-        <v>8592</v>
+        <v>7327</v>
       </c>
       <c r="D6" t="n">
-        <v>1968</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>6319</v>
+        <v>6103</v>
       </c>
       <c r="D7" t="n">
-        <v>801</v>
+        <v>918</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>3201</v>
+        <v>3178</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1190</v>
+        <v>1032</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5615</v>
+        <v>5393</v>
       </c>
       <c r="C2" t="n">
-        <v>8077</v>
+        <v>12444</v>
       </c>
       <c r="D2" t="n">
-        <v>7489</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2495</v>
+        <v>1206</v>
       </c>
       <c r="C2" t="n">
-        <v>3826</v>
+        <v>10059</v>
       </c>
       <c r="D2" t="n">
-        <v>8402</v>
+        <v>16043</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3078</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>4104</v>
+        <v>4229</v>
       </c>
       <c r="D3" t="n">
-        <v>10815</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3497</v>
+        <v>382</v>
       </c>
       <c r="C4" t="n">
-        <v>7995</v>
+        <v>3593</v>
       </c>
       <c r="D4" t="n">
-        <v>9122</v>
+        <v>9370</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1409</v>
+        <v>569</v>
       </c>
       <c r="C5" t="n">
-        <v>11973</v>
+        <v>4963</v>
       </c>
       <c r="D5" t="n">
-        <v>4484</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="C6" t="n">
-        <v>7792</v>
+        <v>6729</v>
       </c>
       <c r="D6" t="n">
-        <v>1647</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>3136</v>
+        <v>6532</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>1166</v>
+        <v>4323</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>1830</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>553</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6399</v>
+        <v>5942</v>
       </c>
       <c r="C2" t="n">
-        <v>4505</v>
+        <v>10732</v>
       </c>
       <c r="D2" t="n">
-        <v>9645</v>
+        <v>22518</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2386</v>
+        <v>1781</v>
       </c>
       <c r="C3" t="n">
-        <v>4070</v>
+        <v>4914</v>
       </c>
       <c r="D3" t="n">
-        <v>1897</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4234</v>
+        <v>3430</v>
       </c>
       <c r="C2" t="n">
-        <v>3333</v>
+        <v>5759</v>
       </c>
       <c r="D2" t="n">
-        <v>10345</v>
+        <v>17571</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3606</v>
+        <v>3264</v>
       </c>
       <c r="C3" t="n">
-        <v>3719</v>
+        <v>7231</v>
       </c>
       <c r="D3" t="n">
-        <v>3059</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1070</v>
+        <v>848</v>
       </c>
       <c r="C4" t="n">
-        <v>2466</v>
+        <v>3115</v>
       </c>
       <c r="D4" t="n">
-        <v>1563</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4219</v>
+        <v>2742</v>
       </c>
       <c r="C2" t="n">
-        <v>5930</v>
+        <v>4770</v>
       </c>
       <c r="D2" t="n">
-        <v>9181</v>
+        <v>24681</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3226</v>
+        <v>2761</v>
       </c>
       <c r="C3" t="n">
-        <v>3036</v>
+        <v>5494</v>
       </c>
       <c r="D3" t="n">
-        <v>4004</v>
+        <v>6637</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1979</v>
+        <v>1807</v>
       </c>
       <c r="C4" t="n">
-        <v>3100</v>
+        <v>5500</v>
       </c>
       <c r="D4" t="n">
-        <v>1802</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>499</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>1465</v>
+        <v>1878</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4515</v>
+        <v>2549</v>
       </c>
       <c r="C2" t="n">
-        <v>8575</v>
+        <v>8198</v>
       </c>
       <c r="D2" t="n">
-        <v>25015</v>
+        <v>27174</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>2274</v>
       </c>
       <c r="C3" t="n">
-        <v>3957</v>
+        <v>4413</v>
       </c>
       <c r="D3" t="n">
-        <v>4509</v>
+        <v>9046</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2202</v>
+        <v>1968</v>
       </c>
       <c r="C4" t="n">
-        <v>3000</v>
+        <v>5382</v>
       </c>
       <c r="D4" t="n">
-        <v>2131</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1033</v>
+        <v>927</v>
       </c>
       <c r="C5" t="n">
-        <v>2297</v>
+        <v>3820</v>
       </c>
       <c r="D5" t="n">
-        <v>1278</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>887</v>
+        <v>1112</v>
       </c>
       <c r="D6" t="n">
-        <v>939</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5563</v>
+        <v>2907</v>
       </c>
       <c r="C2" t="n">
-        <v>11238</v>
+        <v>12218</v>
       </c>
       <c r="D2" t="n">
-        <v>20724</v>
+        <v>33656</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2747</v>
+        <v>1984</v>
       </c>
       <c r="C3" t="n">
-        <v>5208</v>
+        <v>5513</v>
       </c>
       <c r="D3" t="n">
-        <v>6874</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1639</v>
+        <v>1830</v>
       </c>
       <c r="C4" t="n">
-        <v>2900</v>
+        <v>4758</v>
       </c>
       <c r="D4" t="n">
-        <v>2161</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>845</v>
+        <v>1225</v>
       </c>
       <c r="C5" t="n">
-        <v>1931</v>
+        <v>4498</v>
       </c>
       <c r="D5" t="n">
-        <v>1130</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>312</v>
+        <v>494</v>
       </c>
       <c r="C6" t="n">
-        <v>1086</v>
+        <v>2451</v>
       </c>
       <c r="D6" t="n">
-        <v>751</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>396</v>
+        <v>695</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5275</v>
+        <v>2329</v>
       </c>
       <c r="C2" t="n">
-        <v>8877</v>
+        <v>15725</v>
       </c>
       <c r="D2" t="n">
-        <v>19834</v>
+        <v>37213</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3479</v>
+        <v>1963</v>
       </c>
       <c r="C3" t="n">
-        <v>7593</v>
+        <v>7676</v>
       </c>
       <c r="D3" t="n">
-        <v>8794</v>
+        <v>13472</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1934</v>
+        <v>1646</v>
       </c>
       <c r="C4" t="n">
-        <v>4279</v>
+        <v>4983</v>
       </c>
       <c r="D4" t="n">
-        <v>3090</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1108</v>
+        <v>1318</v>
       </c>
       <c r="C5" t="n">
-        <v>2476</v>
+        <v>4529</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>545</v>
+        <v>735</v>
       </c>
       <c r="C6" t="n">
-        <v>1567</v>
+        <v>3369</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>794</v>
+        <v>1479</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>319</v>
+        <v>474</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4307</v>
+        <v>2197</v>
       </c>
       <c r="C2" t="n">
-        <v>6724</v>
+        <v>9938</v>
       </c>
       <c r="D2" t="n">
-        <v>24660</v>
+        <v>29433</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>2740</v>
       </c>
       <c r="C3" t="n">
-        <v>7176</v>
+        <v>11780</v>
       </c>
       <c r="D3" t="n">
-        <v>9927</v>
+        <v>14686</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2322</v>
+        <v>1217</v>
       </c>
       <c r="C4" t="n">
-        <v>6057</v>
+        <v>7361</v>
       </c>
       <c r="D4" t="n">
-        <v>4061</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>679</v>
       </c>
       <c r="C5" t="n">
-        <v>3445</v>
+        <v>3301</v>
       </c>
       <c r="D5" t="n">
-        <v>1597</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>753</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>2045</v>
+        <v>1449</v>
       </c>
       <c r="D6" t="n">
-        <v>883</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>1210</v>
+        <v>464</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
